--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119835382</v>
+        <v>119836122</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119836122</v>
+        <v>119835382</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119836122</v>
+        <v>119837057</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119837057</v>
+        <v>119836809</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119837057</v>
+        <v>119835351</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,21 +2083,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119835382</v>
+        <v>119836809</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119836809</v>
+        <v>119835532</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119835532</v>
+        <v>119837057</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,7 +2067,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119835351</v>
+        <v>119835891</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119835891</v>
+        <v>119835382</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119836809</v>
+        <v>119837057</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119835532</v>
+        <v>119836122</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119837057</v>
+        <v>119835532</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119835382</v>
+        <v>119836122</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119836122</v>
+        <v>119835351</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2361,22 +2361,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119837057</v>
+        <v>119835532</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119835351</v>
+        <v>119837057</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2361,22 +2361,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119835532</v>
+        <v>119835891</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2294,7 +2294,7 @@
         <v>119837057</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 62318-2019 artfynd.xlsx
+++ b/artfynd/A 62318-2019 artfynd.xlsx
@@ -2294,7 +2294,7 @@
         <v>119837057</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
